--- a/docs/StructureDefinition-VAERSLocation.xlsx
+++ b/docs/StructureDefinition-VAERSLocation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.438</t>
+    <t>0.69.439</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-06T17:18:58+00:00</t>
+    <t>2024-12-07T11:18:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSLocation.xlsx
+++ b/docs/StructureDefinition-VAERSLocation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.439</t>
+    <t>0.69.440</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-07T11:18:15+00:00</t>
+    <t>2024-12-08T09:28:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSLocation.xlsx
+++ b/docs/StructureDefinition-VAERSLocation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.440</t>
+    <t>0.69.442</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-08T09:28:43+00:00</t>
+    <t>2024-12-11T20:06:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
